--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19517,7 +19517,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22715,7 +22715,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23921,7 +23921,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24865,16 +24865,16 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O124" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0.07822246403586412</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -25027,10 +25027,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O125" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23716</v>
+        <v>23719</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -2351,7 +2351,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10661,7 +10661,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -16157,7 +16157,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16559,7 +16559,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16961,7 +16961,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17363,7 +17363,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17765,7 +17765,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18167,7 +18167,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -18481,16 +18481,16 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -18643,10 +18643,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20321,7 +20321,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21125,7 +21125,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22715,7 +22715,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23117,7 +23117,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23519,7 +23519,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23921,7 +23921,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25109,7 +25109,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25372,7 +25372,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23719</v>
+        <v>23720</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -24865,16 +24865,16 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q124" t="n">
         <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.09560523382161172</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -25027,10 +25027,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O125" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -25191,6 +25191,408 @@
       <c r="BC125" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>13</v>
+      </c>
+      <c r="O126" t="n">
+        <v>13</v>
+      </c>
+      <c r="P126" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>13</v>
+      </c>
+      <c r="O127" t="n">
+        <v>13</v>
+      </c>
+      <c r="P127" t="n">
+        <v>13</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25227,7 +25629,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -25310,7 +25712,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -25320,7 +25722,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -25340,7 +25742,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -25372,7 +25774,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23720</v>
+        <v>23734</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1320,9 +1317,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1716,9 +1710,6 @@
       <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -2112,9 +2103,6 @@
       <c r="O9" t="n">
         <v>59</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.2563958543397769</v>
       </c>
@@ -2361,7 +2349,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2511,9 +2499,6 @@
       <c r="P11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2763,7 +2748,7 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN12" t="b">
@@ -3165,7 +3150,7 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN14" t="b">
@@ -3567,7 +3552,7 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN16" t="b">
@@ -3969,7 +3954,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN18" t="b">
@@ -4116,9 +4101,6 @@
       <c r="O19" t="n">
         <v>6</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="S19" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4671,9 +4653,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5322,7 +5301,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -5469,9 +5448,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -5865,9 +5841,6 @@
       <c r="O28" t="n">
         <v>42</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.1825190827503496</v>
       </c>
@@ -6114,7 +6087,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6516,7 +6489,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6918,7 +6891,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7320,7 +7293,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7467,9 +7440,6 @@
       <c r="O36" t="n">
         <v>3</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8022,9 +7992,6 @@
       <c r="O39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -8673,7 +8640,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN42" t="b">
@@ -8820,9 +8787,6 @@
       <c r="O43" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.05306927477386519</v>
       </c>
@@ -9216,9 +9180,6 @@
       <c r="O45" t="n">
         <v>50</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.2172846223218448</v>
       </c>
@@ -9465,7 +9426,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN46" t="b">
@@ -9867,7 +9828,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10269,7 +10230,7 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN50" t="b">
@@ -10671,7 +10632,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -11073,7 +11034,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11220,9 +11181,6 @@
       <c r="O55" t="n">
         <v>4</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="S55" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11775,9 +11733,6 @@
       <c r="O58" t="n">
         <v>3</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -12171,9 +12126,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12567,9 +12519,6 @@
       <c r="O62" t="n">
         <v>42</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1825190827503496</v>
       </c>
@@ -12816,7 +12765,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13218,7 +13167,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13620,7 +13569,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14022,7 +13971,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14424,7 +14373,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14571,9 +14520,6 @@
       <c r="O72" t="n">
         <v>5</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="S72" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15126,9 +15072,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -15522,9 +15465,6 @@
       <c r="O77" t="n">
         <v>1</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -15918,9 +15858,6 @@
       <c r="O79" t="n">
         <v>56</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.2433587770004662</v>
       </c>
@@ -16167,7 +16104,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -16569,7 +16506,7 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN82" t="b">
@@ -16971,7 +16908,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -17373,7 +17310,7 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN86" t="b">
@@ -17775,7 +17712,7 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -18177,7 +18114,7 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN90" t="b">
@@ -18486,9 +18423,6 @@
       <c r="O92" t="n">
         <v>1</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -18882,9 +18816,6 @@
       <c r="O94" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.03537951651591013</v>
       </c>
@@ -19278,9 +19209,6 @@
       <c r="O96" t="n">
         <v>51</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.2216303147682817</v>
       </c>
@@ -19527,7 +19455,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19677,9 +19605,6 @@
       <c r="P98" t="n">
         <v>15</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.01225212611348649</v>
       </c>
@@ -19929,7 +19854,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20079,9 +20004,6 @@
       <c r="P100" t="n">
         <v>16</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.01306893452105226</v>
       </c>
@@ -20331,7 +20253,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20481,9 +20403,6 @@
       <c r="P102" t="n">
         <v>21</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.01715297655888109</v>
       </c>
@@ -20733,7 +20652,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20883,9 +20802,6 @@
       <c r="P104" t="n">
         <v>14</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.01143531770592073</v>
       </c>
@@ -21135,7 +21051,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21282,9 +21198,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -21678,9 +21591,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -22074,9 +21984,6 @@
       <c r="O110" t="n">
         <v>56</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.2433587770004662</v>
       </c>
@@ -22323,7 +22230,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22473,9 +22380,6 @@
       <c r="P112" t="n">
         <v>24</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.01960340178157839</v>
       </c>
@@ -22725,7 +22629,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22875,9 +22779,6 @@
       <c r="P114" t="n">
         <v>12</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.009801700890789196</v>
       </c>
@@ -23127,7 +23028,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23277,9 +23178,6 @@
       <c r="P116" t="n">
         <v>12</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.009801700890789196</v>
       </c>
@@ -23529,7 +23427,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23679,9 +23577,6 @@
       <c r="P118" t="n">
         <v>5</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.004084042037828832</v>
       </c>
@@ -23931,7 +23826,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24078,9 +23973,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -24474,9 +24366,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -24865,16 +24754,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O124" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R124" t="n">
-        <v>0.09560523382161172</v>
+        <v>0.1129880036073593</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -25027,10 +24913,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O125" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -25119,7 +25005,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25269,9 +25155,6 @@
       <c r="P126" t="n">
         <v>13</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.01061850929835496</v>
       </c>
@@ -25521,7 +25404,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25774,7 +25657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23734</v>
+        <v>23738</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -24754,13 +24754,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O124" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R124" t="n">
-        <v>0.1129880036073593</v>
+        <v>0.12602508094667</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -24913,10 +24913,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O125" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23738</v>
+        <v>23741</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -24754,13 +24754,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O124" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R124" t="n">
-        <v>0.12602508094667</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -24913,10 +24913,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O125" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23741</v>
+        <v>23742</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -4096,10 +4096,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -4252,10 +4252,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -11176,10 +11176,10 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -11332,10 +11332,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U56" t="inlineStr">
         <is>
@@ -18217,12 +18217,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -18256,25 +18256,19 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>4578</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
-        <v>4578</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>1583</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0.3240112075646558</v>
+        <v>4</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -18284,7 +18278,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
@@ -18294,12 +18288,12 @@
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>SER_CN_AIDS</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AT91" t="n">
@@ -18307,47 +18301,47 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18374,17 +18368,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -18418,29 +18412,104 @@
         </is>
       </c>
       <c r="N92" t="n">
+        <v>4</v>
+      </c>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Acquired immunodeficiency syndrome (AIDS)</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary counts based on the first confirmed AIDS diagnosis in a patient and classified by Diagnosis Status Date. AIDS cases are also included in the HIV series, so the two series are not mutually exclusive.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
         <v>1</v>
       </c>
-      <c r="O92" t="n">
-        <v>1</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_151</t>
-        </is>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -18453,12 +18522,12 @@
       </c>
       <c r="AQ92" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CA_ON_PHO_IDTO_AIDS_MONTHLY</t>
         </is>
       </c>
       <c r="AT92" t="n">
@@ -18466,47 +18535,47 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18533,17 +18602,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -18577,39 +18646,25 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1</v>
+        <v>4578</v>
       </c>
       <c r="O93" t="n">
-        <v>1</v>
+        <v>4578</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>1583</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.3240112075646558</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_151</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>AIDS</t>
-        </is>
-      </c>
-      <c r="Y93" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -18617,67 +18672,9 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG93" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN93" t="b">
-        <v>1</v>
-      </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
@@ -18687,12 +18684,12 @@
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT93" t="n">
@@ -18700,47 +18697,47 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -18772,12 +18769,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -18811,13 +18808,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -18826,7 +18823,7 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -18846,12 +18843,12 @@
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT94" t="n">
@@ -18859,47 +18856,47 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18931,12 +18928,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -18970,29 +18967,29 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -19017,7 +19014,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr">
@@ -19052,17 +19049,17 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19080,12 +19077,12 @@
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT95" t="n">
@@ -19093,47 +19090,47 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -19165,12 +19162,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -19204,13 +19201,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="O96" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="R96" t="n">
-        <v>0.2216303147682817</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -19219,7 +19216,7 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -19244,7 +19241,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT96" t="n">
@@ -19257,42 +19254,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19324,12 +19321,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -19363,29 +19360,29 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="O97" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -19395,7 +19392,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -19410,7 +19407,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr">
@@ -19425,7 +19422,7 @@
       </c>
       <c r="AF97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG97" t="inlineStr">
@@ -19445,17 +19442,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19478,7 +19475,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT97" t="n">
@@ -19491,42 +19488,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19558,12 +19555,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -19588,7 +19585,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -19597,16 +19594,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="O98" t="n">
-        <v>15</v>
-      </c>
-      <c r="P98" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="R98" t="n">
-        <v>0.01225212611348649</v>
+        <v>0.2216303147682817</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19615,12 +19609,12 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -19640,7 +19634,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -19653,42 +19647,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19720,12 +19714,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -19750,7 +19744,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -19759,32 +19753,29 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="O99" t="n">
-        <v>15</v>
-      </c>
-      <c r="P99" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -19799,7 +19790,7 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
@@ -19809,7 +19800,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -19849,7 +19840,7 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -19877,7 +19868,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -19890,42 +19881,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19987,7 +19978,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -19996,16 +19987,16 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P100" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R100" t="n">
-        <v>0.01306893452105226</v>
+        <v>0.01225212611348649</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20149,7 +20140,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -20158,13 +20149,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P101" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -20386,7 +20377,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -20395,16 +20386,16 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="O102" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="P102" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R102" t="n">
-        <v>0.01715297655888109</v>
+        <v>0.01306893452105226</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -20548,7 +20539,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -20557,13 +20548,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="O103" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="P103" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
@@ -20785,7 +20776,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -20794,16 +20785,16 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O104" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P104" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R104" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.01715297655888109</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -20947,7 +20938,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -20956,13 +20947,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="O105" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P105" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
@@ -21154,12 +21145,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -21184,22 +21175,25 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O106" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="P106" t="n">
+        <v>14</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -21208,12 +21202,12 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -21228,12 +21222,12 @@
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -21241,47 +21235,47 @@
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21313,12 +21307,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -21343,33 +21337,36 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c r="P107" t="n">
+        <v>14</v>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
@@ -21384,12 +21381,12 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
@@ -21399,7 +21396,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr">
@@ -21414,7 +21411,7 @@
       </c>
       <c r="AF107" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG107" t="inlineStr">
@@ -21434,12 +21431,12 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -21462,12 +21459,12 @@
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -21475,47 +21472,47 @@
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21547,12 +21544,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -21586,13 +21583,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21601,7 +21598,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -21621,12 +21618,12 @@
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -21634,47 +21631,47 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21706,12 +21703,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -21745,29 +21742,29 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -21792,7 +21789,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -21827,17 +21824,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -21855,12 +21852,12 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -21868,47 +21865,47 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21940,12 +21937,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -21979,13 +21976,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O110" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R110" t="n">
-        <v>0.2433587770004662</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21994,7 +21991,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -22019,7 +22016,7 @@
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -22032,42 +22029,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22099,12 +22096,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -22138,29 +22135,29 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -22170,7 +22167,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -22185,7 +22182,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -22200,7 +22197,7 @@
       </c>
       <c r="AF111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG111" t="inlineStr">
@@ -22220,17 +22217,17 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22253,7 +22250,7 @@
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -22266,42 +22263,42 @@
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22333,12 +22330,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -22363,7 +22360,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -22372,16 +22369,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O112" t="n">
-        <v>24</v>
-      </c>
-      <c r="P112" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="R112" t="n">
-        <v>0.01960340178157839</v>
+        <v>0.2433587770004662</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22390,12 +22384,12 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -22415,7 +22409,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -22428,42 +22422,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22495,12 +22489,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -22525,7 +22519,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -22534,32 +22528,29 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O113" t="n">
-        <v>24</v>
-      </c>
-      <c r="P113" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -22574,7 +22565,7 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
@@ -22584,7 +22575,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -22624,7 +22615,7 @@
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -22652,7 +22643,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -22665,42 +22656,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22762,7 +22753,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -22771,16 +22762,16 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O114" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P114" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R114" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.01960340178157839</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22924,7 +22915,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -22933,13 +22924,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O115" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P115" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
@@ -23161,7 +23152,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -23323,7 +23314,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -23560,7 +23551,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -23569,16 +23560,16 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O118" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P118" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R118" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -23722,7 +23713,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -23731,13 +23722,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O119" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P119" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -23929,12 +23920,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -23959,22 +23950,25 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="P120" t="n">
+        <v>5</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -23983,12 +23977,12 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -24003,12 +23997,12 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -24016,47 +24010,47 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24088,12 +24082,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -24118,33 +24112,36 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="P121" t="n">
+        <v>5</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
@@ -24159,12 +24156,12 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
@@ -24174,7 +24171,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -24189,7 +24186,7 @@
       </c>
       <c r="AF121" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG121" t="inlineStr">
@@ -24209,12 +24206,12 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
@@ -24237,12 +24234,12 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -24250,47 +24247,47 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24322,12 +24319,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -24376,7 +24373,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -24396,12 +24393,12 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -24409,47 +24406,47 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24481,12 +24478,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -24527,22 +24524,22 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -24567,7 +24564,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -24602,17 +24599,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24630,12 +24627,12 @@
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -24643,47 +24640,47 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24715,12 +24712,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -24754,13 +24751,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0.1303707733931069</v>
+        <v>0</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -24769,7 +24766,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -24794,7 +24791,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -24807,42 +24804,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24874,12 +24871,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -24913,29 +24910,29 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -24945,7 +24942,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -24960,7 +24957,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -24975,7 +24972,7 @@
       </c>
       <c r="AF125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG125" t="inlineStr">
@@ -24995,17 +24992,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25028,7 +25025,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -25041,42 +25038,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25108,12 +25105,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -25138,7 +25135,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -25147,16 +25144,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O126" t="n">
-        <v>13</v>
-      </c>
-      <c r="P126" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R126" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -25165,12 +25159,12 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -25190,7 +25184,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -25203,42 +25197,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25270,12 +25264,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -25300,7 +25294,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -25309,32 +25303,29 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O127" t="n">
-        <v>13</v>
-      </c>
-      <c r="P127" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -25349,7 +25340,7 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
@@ -25359,7 +25350,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -25399,7 +25390,7 @@
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -25427,7 +25418,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -25440,40 +25431,439 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>13</v>
+      </c>
+      <c r="O128" t="n">
+        <v>13</v>
+      </c>
+      <c r="P128" t="n">
+        <v>13</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW127" t="inlineStr">
+      <c r="AW128" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX127" t="inlineStr">
+      <c r="AX128" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY127" t="inlineStr">
+      <c r="AY128" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ127" t="inlineStr">
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA127" t="inlineStr">
+      <c r="BA128" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB127" t="inlineStr">
+      <c r="BB128" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC127" t="inlineStr">
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>13</v>
+      </c>
+      <c r="O129" t="n">
+        <v>13</v>
+      </c>
+      <c r="P129" t="n">
+        <v>13</v>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG129" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH129" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM129" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN129" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -25595,7 +25985,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -25605,7 +25995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11">
@@ -25625,7 +26015,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -25657,7 +26047,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23742</v>
+        <v>23744</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -25869,6 +25869,405 @@
         </is>
       </c>
     </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>9</v>
+      </c>
+      <c r="O130" t="n">
+        <v>9</v>
+      </c>
+      <c r="P130" t="n">
+        <v>9</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>9</v>
+      </c>
+      <c r="O131" t="n">
+        <v>9</v>
+      </c>
+      <c r="P131" t="n">
+        <v>9</v>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG131" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN131" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ131" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT131" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25902,7 +26301,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -25985,7 +26384,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -25995,7 +26394,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -26015,7 +26414,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -26047,7 +26446,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23744</v>
+        <v>23753</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -21544,12 +21544,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -21583,13 +21583,16 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="O108" t="n">
-        <v>0</v>
+        <v>4086</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>1526</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>0.2891895574725172</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -21598,7 +21601,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -21608,7 +21611,7 @@
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
@@ -21618,12 +21621,12 @@
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -21631,47 +21634,47 @@
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -21703,12 +21706,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -21742,29 +21745,29 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>4086</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>艾滋病</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -21774,7 +21777,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -21789,7 +21792,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD109" t="inlineStr">
@@ -21804,7 +21807,7 @@
       </c>
       <c r="AF109" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG109" t="inlineStr">
@@ -21824,17 +21827,17 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>China CDC source category 艾滋病; retained as AIDS, not all-stage HIV.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -21842,7 +21845,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
@@ -21852,12 +21855,12 @@
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_CN_AIDS</t>
         </is>
       </c>
       <c r="AT109" t="n">
@@ -21865,47 +21868,47 @@
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -21937,12 +21940,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -21976,13 +21979,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -21991,7 +21994,7 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -22011,12 +22014,12 @@
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT110" t="n">
@@ -22024,47 +22027,47 @@
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22096,12 +22099,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -22135,29 +22138,29 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -22182,7 +22185,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr">
@@ -22217,17 +22220,17 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22245,12 +22248,12 @@
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT111" t="n">
@@ -22258,47 +22261,47 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -22330,12 +22333,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -22369,13 +22372,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0.2433587770004662</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -22384,7 +22387,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -22409,7 +22412,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT112" t="n">
@@ -22422,42 +22425,42 @@
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22489,12 +22492,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -22528,29 +22531,29 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -22560,7 +22563,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -22575,7 +22578,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr">
@@ -22590,7 +22593,7 @@
       </c>
       <c r="AF113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG113" t="inlineStr">
@@ -22610,17 +22613,17 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -22643,7 +22646,7 @@
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT113" t="n">
@@ -22656,42 +22659,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22723,12 +22726,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -22753,7 +22756,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -22762,16 +22765,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O114" t="n">
-        <v>24</v>
-      </c>
-      <c r="P114" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="R114" t="n">
-        <v>0.01960340178157839</v>
+        <v>0.2433587770004662</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -22780,12 +22780,12 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -22805,7 +22805,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT114" t="n">
@@ -22818,42 +22818,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22885,12 +22885,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -22924,32 +22924,29 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O115" t="n">
-        <v>24</v>
-      </c>
-      <c r="P115" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -22964,7 +22961,7 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
@@ -22974,7 +22971,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -23014,7 +23011,7 @@
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -23042,7 +23039,7 @@
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT115" t="n">
@@ -23055,42 +23052,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -23152,7 +23149,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -23161,16 +23158,16 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O116" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P116" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="R116" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.01960340178157839</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -23314,7 +23311,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -23323,13 +23320,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="O117" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P117" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
@@ -23551,7 +23548,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -23713,7 +23710,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -23950,7 +23947,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -23959,16 +23956,16 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O120" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P120" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R120" t="n">
-        <v>0.004084042037828832</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -24112,7 +24109,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -24121,13 +24118,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="O121" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P121" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
@@ -24319,12 +24316,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -24349,22 +24346,25 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="P122" t="n">
+        <v>5</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>0.004084042037828832</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -24373,12 +24373,12 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -24393,12 +24393,12 @@
       </c>
       <c r="AQ122" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -24406,47 +24406,47 @@
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24478,12 +24478,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -24508,33 +24508,36 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="P123" t="n">
+        <v>5</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
@@ -24549,12 +24552,12 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
@@ -24564,7 +24567,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -24579,7 +24582,7 @@
       </c>
       <c r="AF123" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG123" t="inlineStr">
@@ -24599,12 +24602,12 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+          <t>NIID source-reported AIDS series.</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
@@ -24627,12 +24630,12 @@
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_151</t>
+          <t>SER_JP_AIDS_WEEKLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -24640,47 +24643,47 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24712,12 +24715,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -24766,7 +24769,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -24786,12 +24789,12 @@
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -24799,47 +24802,47 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24871,12 +24874,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -24917,22 +24920,22 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>Aids</t>
+          <t>AIDS</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -24957,7 +24960,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -24992,17 +24995,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25020,12 +25023,12 @@
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_701_MONTHLY</t>
+          <t>SER_FI_THL_TTR_151</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -25033,47 +25036,47 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25105,12 +25108,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -25144,13 +25147,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.1303707733931069</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -25159,7 +25162,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -25184,7 +25187,7 @@
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT126" t="n">
@@ -25197,42 +25200,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25264,12 +25267,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -25303,29 +25306,29 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="V127" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>後天免疫缺乏症候群</t>
+          <t>Aids</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -25335,7 +25338,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -25350,7 +25353,7 @@
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr">
@@ -25365,7 +25368,7 @@
       </c>
       <c r="AF127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG127" t="inlineStr">
@@ -25385,17 +25388,17 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>NIDSS disease code 042.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25418,7 +25421,7 @@
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>SER_TW_AIDS_042</t>
+          <t>SER_NO_FHI_701_MONTHLY</t>
         </is>
       </c>
       <c r="AT127" t="n">
@@ -25431,42 +25434,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25498,12 +25501,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -25528,7 +25531,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -25537,16 +25540,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O128" t="n">
-        <v>13</v>
-      </c>
-      <c r="P128" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="R128" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25555,12 +25555,12 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -25580,7 +25580,7 @@
       </c>
       <c r="AS128" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT128" t="n">
@@ -25593,42 +25593,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25660,12 +25660,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -25690,7 +25690,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -25699,32 +25699,29 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="O129" t="n">
-        <v>13</v>
-      </c>
-      <c r="P129" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="V129" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>AIDS</t>
+          <t>後天免疫缺乏症候群</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -25739,7 +25736,7 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
@@ -25749,7 +25746,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr">
@@ -25789,7 +25786,7 @@
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>NIID source-reported AIDS series.</t>
+          <t>NIDSS disease code 042.</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -25817,7 +25814,7 @@
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>SER_JP_AIDS_WEEKLY</t>
+          <t>SER_TW_AIDS_042</t>
         </is>
       </c>
       <c r="AT129" t="n">
@@ -25830,42 +25827,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25927,7 +25924,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -25936,16 +25933,16 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O130" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P130" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R130" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.01061850929835496</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -26089,7 +26086,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -26098,13 +26095,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O131" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P131" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -26263,6 +26260,405 @@
         </is>
       </c>
       <c r="BC131" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>9</v>
+      </c>
+      <c r="O132" t="n">
+        <v>9</v>
+      </c>
+      <c r="P132" t="n">
+        <v>9</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP132" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ132" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT132" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU132" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA132" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB132" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC132" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>9</v>
+      </c>
+      <c r="O133" t="n">
+        <v>9</v>
+      </c>
+      <c r="P133" t="n">
+        <v>9</v>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG133" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM133" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN133" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP133" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ133" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU133" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA133" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB133" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC133" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -26384,7 +26780,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -26394,7 +26790,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -26414,7 +26810,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -26424,7 +26820,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -26446,7 +26842,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23753</v>
+        <v>27839</v>
       </c>
     </row>
     <row r="16">
@@ -26456,7 +26852,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8974</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -25147,13 +25147,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -25306,10 +25306,10 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27839</v>
+        <v>27840</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -26664,6 +26664,405 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>14</v>
+      </c>
+      <c r="O134" t="n">
+        <v>14</v>
+      </c>
+      <c r="P134" t="n">
+        <v>14</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU134" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV134" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA134" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB134" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC134" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>14</v>
+      </c>
+      <c r="O135" t="n">
+        <v>14</v>
+      </c>
+      <c r="P135" t="n">
+        <v>14</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26697,7 +27096,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -26780,7 +27179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -26790,7 +27189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -26810,7 +27209,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -26842,7 +27241,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27840</v>
+        <v>27854</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10220,7 +10220,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13559,7 +13559,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -16094,7 +16094,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18104,7 +18104,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19835,7 +19835,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20633,7 +20633,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21032,7 +21032,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21431,7 +21431,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23006,7 +23006,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24203,7 +24203,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26180,7 +26180,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26978,7 +26978,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">

--- a/diseases/d005/2026-2029.xlsx
+++ b/diseases/d005/2026-2029.xlsx
@@ -48012,13 +48012,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R244" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -48176,10 +48176,10 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U245" t="inlineStr">
         <is>
@@ -49935,6 +49935,1211 @@
       <c r="BC253" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>15</v>
+      </c>
+      <c r="O254" t="n">
+        <v>15</v>
+      </c>
+      <c r="P254" t="n">
+        <v>15</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.01225212611348649</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>15</v>
+      </c>
+      <c r="O255" t="n">
+        <v>15</v>
+      </c>
+      <c r="P255" t="n">
+        <v>15</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>NIID source-reported AIDS series.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_JP_AIDS_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT255" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ256" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT256" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA256" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB256" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC256" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB257" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC257" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD257" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE257" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF257" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG257" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH257" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI257" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ257" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Independent AIDS series; never add to HIV total.</t>
+        </is>
+      </c>
+      <c r="AM257" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN257" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ257" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_151</t>
+        </is>
+      </c>
+      <c r="AT257" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>1</v>
+      </c>
+      <c r="O258" t="n">
+        <v>1</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ258" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT258" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>aids</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D005</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>AIDS</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>艾滋病</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>1</v>
+      </c>
+      <c r="O259" t="n">
+        <v>1</v>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>Aids</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB259" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC259" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD259" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE259" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF259" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG259" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH259" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI259" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ259" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS AIDS category kept distinct from all-stage HIV.</t>
+        </is>
+      </c>
+      <c r="AM259" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN259" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ259" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_701_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT259" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -49971,7 +51176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -50054,7 +51259,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
@@ -50064,7 +51269,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -50084,7 +51289,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -50116,7 +51321,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40600</v>
+        <v>40617</v>
       </c>
     </row>
     <row r="16">
